--- a/Entregables II/4.Normalizacion y Modelo Relacional/Normalizacion.xlsx
+++ b/Entregables II/4.Normalizacion y Modelo Relacional/Normalizacion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1927\Desktop\carpeta\Documents\Proyecto\Entregables II\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1927\Desktop\carpeta\Documents\Proyecto\Entregables II\4.Normalizacion y Modelo Relacional\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB78B8E-FDCF-4CF6-BD84-FF6DCD016557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B129806-1B8D-4B79-91E9-ADC034053C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13290" xr2:uid="{12832E4A-EB5C-4BF4-8015-36C482B4E8FE}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="156">
   <si>
     <t>Correo</t>
   </si>
@@ -96,12 +96,6 @@
     <t>idReporte</t>
   </si>
   <si>
-    <t>Usuario</t>
-  </si>
-  <si>
-    <t>Habito</t>
-  </si>
-  <si>
     <t>Recordatorio</t>
   </si>
   <si>
@@ -120,9 +114,6 @@
     <t>Comentarios</t>
   </si>
   <si>
-    <t>Administrador</t>
-  </si>
-  <si>
     <t>idAdmin</t>
   </si>
   <si>
@@ -174,9 +165,6 @@
     <t>Frecuencia</t>
   </si>
   <si>
-    <t>Comenatario</t>
-  </si>
-  <si>
     <t>idComenatrio</t>
   </si>
   <si>
@@ -189,18 +177,9 @@
     <t>Tabla sin normalizar</t>
   </si>
   <si>
-    <t>Seguimiento</t>
-  </si>
-  <si>
     <t>idSeguimiento</t>
   </si>
   <si>
-    <t>Rol</t>
-  </si>
-  <si>
-    <t>Planeamiento</t>
-  </si>
-  <si>
     <t>idRol</t>
   </si>
   <si>
@@ -300,9 +279,6 @@
     <t>Fitness</t>
   </si>
   <si>
-    <t>Elías N.</t>
-  </si>
-  <si>
     <t>elias.n@gym.com</t>
   </si>
   <si>
@@ -315,9 +291,6 @@
     <t>Nutrición</t>
   </si>
   <si>
-    <t>Sofía R.</t>
-  </si>
-  <si>
     <t>sofia.r@food.com</t>
   </si>
   <si>
@@ -327,9 +300,6 @@
     <t>A901</t>
   </si>
   <si>
-    <t>Miguel V.</t>
-  </si>
-  <si>
     <t>miguel@admin.com</t>
   </si>
   <si>
@@ -339,9 +309,6 @@
     <t>A902</t>
   </si>
   <si>
-    <t>Laura M.</t>
-  </si>
-  <si>
     <t>laura@admin.com</t>
   </si>
   <si>
@@ -457,6 +424,87 @@
   </si>
   <si>
     <t>Mejorar resistencia cardiovascular.</t>
+  </si>
+  <si>
+    <t>Apellido</t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>Esteban</t>
+  </si>
+  <si>
+    <t>Leon</t>
+  </si>
+  <si>
+    <t>Velasquez</t>
+  </si>
+  <si>
+    <t>Usuarios</t>
+  </si>
+  <si>
+    <t>Habitos</t>
+  </si>
+  <si>
+    <t>Foros</t>
+  </si>
+  <si>
+    <t>Entrenadores</t>
+  </si>
+  <si>
+    <t>Administradores</t>
+  </si>
+  <si>
+    <t>Rankings</t>
+  </si>
+  <si>
+    <t>Seguimientos</t>
+  </si>
+  <si>
+    <t>Recordatorios</t>
+  </si>
+  <si>
+    <t>Comenatarios</t>
+  </si>
+  <si>
+    <t>Roles</t>
+  </si>
+  <si>
+    <t>Planeamientos</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>Duque</t>
+  </si>
+  <si>
+    <t>Laura</t>
+  </si>
+  <si>
+    <t>Marisol</t>
+  </si>
+  <si>
+    <t>Elías</t>
+  </si>
+  <si>
+    <t>Nairo</t>
+  </si>
+  <si>
+    <t>Sofía</t>
+  </si>
+  <si>
+    <t>Rodriguez</t>
+  </si>
+  <si>
+    <t>EstadoAdmin</t>
+  </si>
+  <si>
+    <t>Activo</t>
+  </si>
+  <si>
+    <t>Ausente</t>
   </si>
 </sst>
 </file>
@@ -665,7 +713,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -725,12 +773,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
@@ -750,9 +829,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -825,120 +901,6 @@
     <xf numFmtId="0" fontId="4" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -951,23 +913,134 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1298,17 +1371,16 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="5"/>
-    <col min="2" max="2" width="14.85546875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" style="5" customWidth="1"/>
+    <col min="2" max="3" width="14.85546875" style="5" customWidth="1"/>
     <col min="4" max="4" width="43.28515625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="45.140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="36.7109375" style="5" customWidth="1"/>
     <col min="6" max="6" width="16.42578125" style="5" customWidth="1"/>
     <col min="7" max="7" width="16.5703125" style="5" customWidth="1"/>
     <col min="8" max="8" width="16.42578125" style="5" customWidth="1"/>
     <col min="9" max="9" width="16.85546875" style="5" customWidth="1"/>
     <col min="10" max="10" width="16" style="5" customWidth="1"/>
     <col min="11" max="11" width="15.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" style="5" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" style="5" customWidth="1"/>
     <col min="13" max="13" width="15.42578125" style="5" customWidth="1"/>
     <col min="14" max="14" width="15.85546875" style="5" customWidth="1"/>
     <col min="15" max="15" width="18.42578125" style="5" customWidth="1"/>
@@ -1318,50 +1390,50 @@
     <col min="19" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="57"/>
-    </row>
-    <row r="4" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B4" s="12" t="s">
+    <row r="2" spans="2:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="B2" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="37"/>
+    </row>
+    <row r="4" spans="2:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="B4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" ht="15" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="70" t="s">
-        <v>61</v>
+        <v>58</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>54</v>
       </c>
       <c r="E5" s="2">
         <v>1500</v>
@@ -1370,7 +1442,7 @@
         <v>5</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H5" s="2">
         <v>12</v>
@@ -1382,15 +1454,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" ht="15" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="70" t="s">
-        <v>63</v>
+        <v>59</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>56</v>
       </c>
       <c r="E6" s="2">
         <v>850</v>
@@ -1399,7 +1471,7 @@
         <v>18</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H6" s="2">
         <v>5</v>
@@ -1411,161 +1483,173 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B9" s="11" t="s">
+    <row r="9" spans="2:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="B9" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B11" s="12" t="s">
+    <row r="11" spans="2:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="B11" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="66" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="F11" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="G11" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="H11" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="I11" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="J11" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="K11" s="11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" ht="15" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>101</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="2">
+        <v>130</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E12" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="2">
         <v>1500</v>
       </c>
-      <c r="F12" s="2">
+      <c r="G12" s="2">
         <v>5</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H12" s="2">
+      <c r="H12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12" s="2">
         <v>12</v>
       </c>
-      <c r="I12" s="2">
+      <c r="J12" s="2">
         <v>45</v>
       </c>
-      <c r="J12" s="2">
+      <c r="K12" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" ht="15" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>102</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="70" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" s="2">
+        <v>131</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="2">
         <v>850</v>
       </c>
-      <c r="F13" s="2">
+      <c r="G13" s="2">
         <v>18</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="2">
+      <c r="H13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I13" s="2">
         <v>5</v>
       </c>
-      <c r="I13" s="2">
+      <c r="J13" s="2">
         <v>102</v>
       </c>
-      <c r="J13" s="2">
+      <c r="K13" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B16" s="11" t="s">
+    <row r="16" spans="2:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="67" t="s">
+        <v>134</v>
+      </c>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68"/>
+      <c r="K18" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="L18" s="45"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="45"/>
+      <c r="P18" s="46"/>
+    </row>
+    <row r="19" spans="2:16" ht="15" x14ac:dyDescent="0.25">
+      <c r="B19" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="M19" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="N19" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="O19" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="74"/>
-      <c r="K18" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L18" s="39"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="39"/>
-      <c r="P18" s="40"/>
-    </row>
-    <row r="19" spans="2:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="B19" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="L19" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="M19" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="N19" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="O19" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="P19" s="78" t="s">
+      <c r="P19" s="35" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1574,36 +1658,39 @@
         <v>101</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H20" s="2">
+        <v>5</v>
+      </c>
+      <c r="I20" s="2">
+        <v>12</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="M20" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N20" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20" s="2">
-        <v>5</v>
-      </c>
-      <c r="H20" s="2">
-        <v>12</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="O20" s="71">
+      <c r="O20" s="32">
         <v>0.33333333333333331</v>
       </c>
       <c r="P20" s="6">
@@ -1615,36 +1702,39 @@
         <v>102</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="H21" s="2">
+        <v>18</v>
+      </c>
+      <c r="I21" s="6">
+        <v>5</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L21" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="M21" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G21" s="2">
-        <v>18</v>
-      </c>
-      <c r="H21" s="6">
-        <v>5</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="N21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="O21" s="71">
+        <v>71</v>
+      </c>
+      <c r="O21" s="32">
         <v>0.75</v>
       </c>
       <c r="P21" s="6">
@@ -1659,293 +1749,323 @@
       <c r="O22" s="4"/>
     </row>
     <row r="23" spans="2:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="67" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="68"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="69"/>
-      <c r="H23" s="61" t="s">
-        <v>29</v>
-      </c>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="62"/>
-      <c r="M23" s="63"/>
+      <c r="B23" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="43"/>
+      <c r="H23" s="71" t="s">
+        <v>137</v>
+      </c>
+      <c r="I23" s="71"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="71"/>
+      <c r="L23" s="71"/>
+      <c r="M23" s="71"/>
+      <c r="N23" s="71"/>
     </row>
     <row r="24" spans="2:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="16" t="s">
+      <c r="F24" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J24" s="19" t="s">
+      <c r="H24" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="J24" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="19" t="s">
+      <c r="K24" s="25"/>
+      <c r="L24" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="L24" s="20" t="s">
+      <c r="M24" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="N24" s="18" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="25" spans="2:16" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" s="72">
+        <v>74</v>
+      </c>
+      <c r="E25" s="33">
         <v>45955</v>
       </c>
       <c r="F25" s="6">
         <v>15</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>88</v>
+        <v>150</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>70</v>
+        <v>81</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="2:16" ht="42.75" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E26" s="72">
+        <v>77</v>
+      </c>
+      <c r="E26" s="33">
         <v>45958</v>
       </c>
       <c r="F26" s="6">
         <v>32</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>68</v>
+        <v>85</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="2:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="B28" s="58" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" s="59"/>
-      <c r="D28" s="59"/>
-      <c r="E28" s="59"/>
-      <c r="F28" s="60"/>
-      <c r="H28" s="64" t="s">
+      <c r="B28" s="69" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="74"/>
+      <c r="J28" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="I28" s="65"/>
-      <c r="J28" s="65"/>
-      <c r="K28" s="66"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="40"/>
     </row>
     <row r="29" spans="2:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="B29" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="22" t="s">
+      <c r="B29" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="E29" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="F29" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="F29" s="22" t="s">
+      <c r="G29" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="H29" s="24" t="s">
+      <c r="H29" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="J29" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="K29" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="L29" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="M29" s="23" t="s">
         <v>32</v>
-      </c>
-      <c r="I29" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="J29" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="K29" s="24" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>70</v>
+        <v>87</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G30" s="73" t="s">
+        <v>63</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="K30" s="73">
+        <v>92</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M30" s="34">
         <v>45935</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>68</v>
+        <v>90</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="73" t="s">
+        <v>61</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="K31" s="73">
+        <v>95</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="M31" s="34">
         <v>45940</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="B34" s="11" t="s">
-        <v>36</v>
+      <c r="B34" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="B36" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="C36" s="77"/>
-      <c r="D36" s="77"/>
-      <c r="E36" s="77"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
-      <c r="I36" s="77"/>
-      <c r="J36" s="74"/>
-      <c r="K36" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L36" s="39"/>
-      <c r="M36" s="39"/>
-      <c r="N36" s="39"/>
-      <c r="O36" s="40"/>
+      <c r="B36" s="67" t="s">
+        <v>134</v>
+      </c>
+      <c r="C36" s="68"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="68"/>
+      <c r="H36" s="68"/>
+      <c r="I36" s="68"/>
+      <c r="J36" s="68"/>
+      <c r="L36" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="M36" s="45"/>
+      <c r="N36" s="45"/>
+      <c r="O36" s="45"/>
+      <c r="P36" s="46"/>
     </row>
     <row r="37" spans="2:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="E37" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="E37" s="25" t="s">
+      <c r="F37" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="G37" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="H37" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="H37" s="13" t="s">
+      <c r="I37" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="I37" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="J37" s="75"/>
-      <c r="K37" s="15" t="s">
+      <c r="J37" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="L37" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="L37" s="15" t="s">
+      <c r="M37" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="M37" s="15" t="s">
+      <c r="N37" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="N37" s="15" t="s">
+      <c r="O37" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="O37" s="78" t="s">
+      <c r="P37" s="35" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1954,40 +2074,42 @@
         <v>101</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I38" s="2">
+        <v>12</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M38" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E38" s="2" t="s">
+      <c r="N38" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="O38" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H38" s="2">
-        <v>12</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="J38" s="76"/>
-      <c r="K38" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="O38" s="6">
+      <c r="P38" s="6">
         <v>10</v>
       </c>
     </row>
@@ -1996,40 +2118,42 @@
         <v>102</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D39" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="H39" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I39" s="2">
+        <v>5</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M39" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="N39" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H39" s="2">
-        <v>5</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="J39" s="76"/>
-      <c r="K39" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="O39" s="6">
+      <c r="O39" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="P39" s="6">
         <v>10</v>
       </c>
     </row>
@@ -2041,119 +2165,125 @@
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="2:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="B41" s="50" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" s="50"/>
-      <c r="D41" s="50"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="61" t="s">
-        <v>29</v>
-      </c>
-      <c r="H41" s="62"/>
-      <c r="I41" s="62"/>
-      <c r="J41" s="62"/>
-      <c r="K41" s="62"/>
-      <c r="L41" s="63"/>
+      <c r="B41" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41" s="59"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="71" t="s">
+        <v>137</v>
+      </c>
+      <c r="H41" s="71"/>
+      <c r="I41" s="71"/>
+      <c r="J41" s="75"/>
+      <c r="K41" s="76" t="s">
+        <v>138</v>
+      </c>
+      <c r="L41" s="76"/>
+      <c r="M41" s="76"/>
     </row>
     <row r="42" spans="2:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C42" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D42" s="16" t="s">
+      <c r="F42" s="9"/>
+      <c r="G42" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="H42" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="I42" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="J42" s="77"/>
+      <c r="K42" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="F42" s="10"/>
-      <c r="G42" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="H42" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="I42" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="J42" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="K42" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="L42" s="19" t="s">
-        <v>10</v>
+      <c r="L42" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="M42" s="21" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="2:16" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E43" s="33">
+        <v>45955</v>
+      </c>
+      <c r="F43" s="8"/>
+      <c r="G43" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E43" s="72">
-        <v>45955</v>
-      </c>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="H43" s="6" t="s">
+      <c r="I43" s="6">
+        <v>104</v>
+      </c>
+      <c r="J43" s="8"/>
+      <c r="K43" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="I43" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J43" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="K43" s="6" t="s">
-        <v>89</v>
-      </c>
       <c r="L43" s="6" t="s">
-        <v>70</v>
+        <v>154</v>
+      </c>
+      <c r="M43" s="6">
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="2:16" ht="42.75" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E44" s="33">
+        <v>45958</v>
+      </c>
+      <c r="F44" s="8"/>
+      <c r="G44" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="H44" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E44" s="72">
-        <v>45958</v>
-      </c>
-      <c r="F44" s="9"/>
-      <c r="G44" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="J44" s="6" t="s">
-        <v>93</v>
-      </c>
+      <c r="I44" s="6">
+        <v>106</v>
+      </c>
+      <c r="J44" s="8"/>
       <c r="K44" s="6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>68</v>
+        <v>155</v>
+      </c>
+      <c r="M44" s="6">
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="2:16" ht="15" x14ac:dyDescent="0.25">
@@ -2161,431 +2291,379 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="9"/>
-      <c r="K45" s="9"/>
-      <c r="M45" s="9"/>
-      <c r="N45" s="9"/>
-      <c r="O45" s="9"/>
-      <c r="P45" s="9"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="8"/>
+      <c r="O45" s="8"/>
+      <c r="P45" s="8"/>
     </row>
     <row r="46" spans="2:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="B46" s="58" t="s">
+      <c r="B46" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="39"/>
+      <c r="D46" s="39"/>
+      <c r="E46" s="40"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="H46" s="54"/>
+      <c r="I46" s="55"/>
+      <c r="K46" s="60" t="s">
+        <v>140</v>
+      </c>
+      <c r="L46" s="61"/>
+      <c r="M46" s="61"/>
+      <c r="N46" s="61"/>
+      <c r="O46" s="62"/>
+    </row>
+    <row r="47" spans="2:16" ht="15" x14ac:dyDescent="0.25">
+      <c r="B47" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E47" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" s="8"/>
+      <c r="G47" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="I47" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="K47" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="L47" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="M47" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="N47" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="O47" s="26" t="s">
         <v>27</v>
-      </c>
-      <c r="C46" s="59"/>
-      <c r="D46" s="59"/>
-      <c r="E46" s="59"/>
-      <c r="F46" s="60"/>
-      <c r="H46" s="64" t="s">
-        <v>6</v>
-      </c>
-      <c r="I46" s="65"/>
-      <c r="J46" s="65"/>
-      <c r="K46" s="66"/>
-      <c r="L46" s="9"/>
-      <c r="M46" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="N46" s="45"/>
-      <c r="O46" s="46"/>
-    </row>
-    <row r="47" spans="2:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="B47" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C47" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E47" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="H47" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="I47" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="J47" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="K47" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="L47" s="9"/>
-      <c r="M47" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="N47" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="O47" s="26" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B48" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E48" s="34">
+        <v>45935</v>
+      </c>
+      <c r="F48" s="8"/>
+      <c r="G48" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H48" s="6">
+        <v>1</v>
+      </c>
+      <c r="I48" s="6">
+        <v>3200</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="L48" s="34">
+        <v>45971</v>
+      </c>
+      <c r="M48" s="36">
+        <v>0.85</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="O48" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B49" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C49" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D49" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E49" s="34">
+        <v>45940</v>
+      </c>
+      <c r="F49" s="8"/>
+      <c r="G49" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F48" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="H48" s="6" t="s">
+      <c r="H49" s="6">
+        <v>5</v>
+      </c>
+      <c r="I49" s="6">
+        <v>1500</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="L49" s="34">
+        <v>45976</v>
+      </c>
+      <c r="M49" s="36">
+        <v>0.6</v>
+      </c>
+      <c r="N49" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="O49" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51" spans="2:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B51" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="C51" s="64"/>
+      <c r="D51" s="64"/>
+      <c r="E51" s="65"/>
+      <c r="G51" s="56" t="s">
+        <v>142</v>
+      </c>
+      <c r="H51" s="57"/>
+      <c r="I51" s="57"/>
+      <c r="J51" s="58"/>
+    </row>
+    <row r="52" spans="2:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B52" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="D52" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="E52" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="H52" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="I52" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="J52" s="28" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B53" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I53" s="34">
+        <v>45956</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B54" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="I54" s="34">
+        <v>45959</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" spans="2:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B56" s="47" t="s">
+        <v>143</v>
+      </c>
+      <c r="C56" s="48"/>
+      <c r="D56" s="48"/>
+      <c r="E56" s="49"/>
+      <c r="G56" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="H56" s="51"/>
+      <c r="I56" s="51"/>
+      <c r="J56" s="51"/>
+      <c r="K56" s="51"/>
+      <c r="L56" s="52"/>
+    </row>
+    <row r="57" spans="2:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B57" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C57" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D57" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="G57" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="H57" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="I57" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="J57" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="K57" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="L57" s="30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B58" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D58" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="I48" s="6" t="s">
+      <c r="E58" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B59" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D59" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="J48" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="K48" s="73">
-        <v>45935</v>
-      </c>
-      <c r="L48" s="9"/>
-      <c r="M48" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="N48" s="6">
-        <v>1</v>
-      </c>
-      <c r="O48" s="6">
-        <v>3200</v>
-      </c>
-    </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B49" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="H49" s="6" t="s">
+      <c r="E59" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I49" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="J49" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="K49" s="73">
-        <v>45940</v>
-      </c>
-      <c r="L49" s="9"/>
-      <c r="M49" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="N49" s="6">
-        <v>5</v>
-      </c>
-      <c r="O49" s="6">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="51" spans="2:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="B51" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="C51" s="52"/>
-      <c r="D51" s="52"/>
-      <c r="E51" s="52"/>
-      <c r="F51" s="53"/>
-      <c r="H51" s="54" t="s">
-        <v>21</v>
-      </c>
-      <c r="I51" s="55"/>
-      <c r="J51" s="55"/>
-      <c r="K51" s="56"/>
-      <c r="M51" s="47" t="s">
-        <v>45</v>
-      </c>
-      <c r="N51" s="48"/>
-      <c r="O51" s="48"/>
-      <c r="P51" s="49"/>
-    </row>
-    <row r="52" spans="2:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="B52" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C52" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="D52" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="E52" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="F52" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="H52" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="I52" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="J52" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="K52" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M52" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="N52" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="O52" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="P52" s="29" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B53" s="6" t="s">
+      <c r="G59" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="J59" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C53" s="73">
-        <v>45971</v>
-      </c>
-      <c r="D53" s="79">
-        <v>0.85</v>
-      </c>
-      <c r="E53" s="6" t="s">
+      <c r="K59" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="F53" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="J53" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="K53" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M53" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="N53" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="O53" s="73">
-        <v>45956</v>
-      </c>
-      <c r="P53" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B54" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C54" s="73">
-        <v>45976</v>
-      </c>
-      <c r="D54" s="79">
-        <v>0.6</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="J54" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="K54" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="M54" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="N54" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="O54" s="73">
-        <v>45959</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="56" spans="2:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="B56" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="C56" s="33"/>
-      <c r="D56" s="33"/>
-      <c r="E56" s="34"/>
-      <c r="G56" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="H56" s="36"/>
-      <c r="I56" s="36"/>
-      <c r="J56" s="36"/>
-      <c r="K56" s="36"/>
-      <c r="L56" s="37"/>
-    </row>
-    <row r="57" spans="2:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="B57" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="C57" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D57" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="E57" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="G57" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="H57" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="I57" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="J57" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="K57" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="L57" s="31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B58" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="J58" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K58" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="L58" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B59" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="H59" s="6" t="s">
+      <c r="L59" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="J59" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="K59" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="L59" s="6" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="G41:L41"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="H28:K28"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="K36:O36"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="K18:P18"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="G46:I46"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="B46:E46"/>
     <mergeCell ref="B56:E56"/>
     <mergeCell ref="G56:L56"/>
-    <mergeCell ref="M46:O46"/>
-    <mergeCell ref="M51:P51"/>
+    <mergeCell ref="G51:J51"/>
     <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="H51:K51"/>
+    <mergeCell ref="K46:O46"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="K18:P18"/>
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="L36:P36"/>
+    <mergeCell ref="B36:J36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
